--- a/data/processed/Volatility Risk Index.xlsx
+++ b/data/processed/Volatility Risk Index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10114"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bocconi.sharepoint.com/sites/Geopolitics-DataGroup1/Documenti condivisi/General/Final Dataset - CGPR/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{AE97D769-5EB8-814F-9D37-A7775E5C110A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB2D1732-9040-7D4B-AEAF-A7E5DD6A53E6}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{AE97D769-5EB8-814F-9D37-A7775E5C110A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{953DB980-CF40-F449-AC2E-F6DCDEA506C7}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{C066B819-EFB4-944B-8BE5-E6E5411F9C06}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{C066B819-EFB4-944B-8BE5-E6E5411F9C06}"/>
   </bookViews>
   <sheets>
     <sheet name="Volatility Risk Index" sheetId="1" r:id="rId1"/>
@@ -243,7 +243,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="13">
     <dxf>
@@ -467,6 +467,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -53124,12 +53128,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -53138,9 +53136,15 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100086DC0FFDEFA864DA147FFDEA823F2EE" ma:contentTypeVersion="3" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="efa000e167d9ce5db8cd2eb5b6f87cd4">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c41a64fd-65ba-4a6e-8004-8ade4c8fdb39" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f94584ddf2c7798ba84aeef6e679263" ns2:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100086DC0FFDEFA864DA147FFDEA823F2EE" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="39870545afabb502c4050089500bd5b6">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c41a64fd-65ba-4a6e-8004-8ade4c8fdb39" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9bb2a11c505461e40f497f8b9cdcbcf5" ns2:_="">
     <xsd:import namespace="c41a64fd-65ba-4a6e-8004-8ade4c8fdb39"/>
     <xsd:element name="properties">
       <xsd:complexType>
@@ -53186,8 +53190,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo di contenuto"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titolo"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -53277,22 +53281,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89DDF7E6-7BCE-4001-8A23-B96ADE076CA8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="c41a64fd-65ba-4a6e-8004-8ade4c8fdb39"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{360BEE6B-753E-443A-8511-E7C808938A1D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -53300,20 +53288,22 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA3B4E71-FD66-4E2F-977E-297A295D1952}">
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89DDF7E6-7BCE-4001-8A23-B96ADE076CA8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="c41a64fd-65ba-4a6e-8004-8ade4c8fdb39"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A3378BF-71D7-4CD4-B9ED-E2781FE364F2}"/>
 </file>